--- a/public/designer-data/challenge_stage_content.xlsx
+++ b/public/designer-data/challenge_stage_content.xlsx
@@ -123,10 +123,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,10 +158,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -597,10 +597,10 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v/>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2" t="str">
         <v>CH-1</v>
@@ -686,10 +686,10 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3" t="str">
         <v>CH-2</v>
@@ -775,10 +775,10 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v/>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4" t="str">
         <v>CH-3</v>
@@ -796,7 +796,7 @@
         <v>老瞎眼、寒光智者、寒光先知、鱼人领军、鱼人斥候</v>
       </c>
       <c r="Z4" t="str">
-        <v>8slot_0</v>
+        <v>standard_5slot</v>
       </c>
       <c r="AA4" t="str">
         <v>挑战怒吼,盾牌格挡,盾牌反射,无视苦痛,盾墙,盾牌猛击,复仇</v>
@@ -864,10 +864,10 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v/>
-      </c>
-      <c r="T5" t="str">
-        <v/>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection</v>
+      </c>
+      <c r="T5">
+        <v>2</v>
       </c>
       <c r="U5" t="str">
         <v>CH-4</v>
@@ -885,7 +885,7 @@
         <v>狗头人学徒、鱼人猎潮者、鱼人吹箭者、鱼人斥候</v>
       </c>
       <c r="Z5" t="str">
-        <v>standard_5slot</v>
+        <v>8slot_0</v>
       </c>
       <c r="AA5" t="str">
         <v/>
@@ -953,10 +953,10 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v/>
-      </c>
-      <c r="T6" t="str">
-        <v/>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection</v>
+      </c>
+      <c r="T6">
+        <v>2</v>
       </c>
       <c r="U6" t="str">
         <v>CH-5</v>
@@ -974,7 +974,7 @@
         <v>狗头人拾荒者、寒光先知、寒光智者、鱼人斥候</v>
       </c>
       <c r="Z6" t="str">
-        <v>standard_5slot</v>
+        <v>8slot_0</v>
       </c>
       <c r="AA6" t="str">
         <v>拳击,盾牌反射,无视苦痛,盾牌猛击,盾牌格挡</v>
@@ -1042,10 +1042,10 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v/>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection</v>
+      </c>
+      <c r="T7">
+        <v>2</v>
       </c>
       <c r="U7" t="str">
         <v>CH-6</v>
@@ -1134,7 +1134,7 @@
         <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout</v>
       </c>
       <c r="T8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U8" t="str">
         <v>CH-7</v>
@@ -1152,7 +1152,7 @@
         <v>巨魔狂战士、巨魔猎头者、寒光先知、寒光智者</v>
       </c>
       <c r="Z8" t="str">
-        <v>standard_5slot</v>
+        <v>8slot_2</v>
       </c>
       <c r="AA8" t="str">
         <v>挑战怒吼,拳击,盾牌格挡,无视苦痛,盾牌猛击</v>
@@ -1223,7 +1223,7 @@
         <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout</v>
       </c>
       <c r="T9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U9" t="str">
         <v>CH-8</v>
@@ -1241,7 +1241,7 @@
         <v>森林巨魔狂战士、巨魔高阶牧师、寒光先知、寒光智者</v>
       </c>
       <c r="Z9" t="str">
-        <v>8slot_0</v>
+        <v>8slot_2</v>
       </c>
       <c r="AA9" t="str">
         <v>挑战怒吼,拳击,盾牌反射,无视苦痛,盾牌格挡,盾牌猛击</v>
@@ -1312,7 +1312,7 @@
         <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout</v>
       </c>
       <c r="T10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U10" t="str">
         <v>CH-9</v>
@@ -1330,7 +1330,7 @@
         <v>巨魔督军、巨魔持盾卫士、巨魔高阶牧师</v>
       </c>
       <c r="Z10" t="str">
-        <v>8slot_0</v>
+        <v>8slot_2</v>
       </c>
       <c r="AA10" t="str">
         <v>挑战怒吼,拳击,盾牌格挡,无视苦痛,盾墙,复仇</v>

--- a/public/designer-data/challenge_stage_content.xlsx
+++ b/public/designer-data/challenge_stage_content.xlsx
@@ -123,10 +123,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,10 +158,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -558,7 +558,7 @@
         <v>鱼人前排与基础读条混编，验证起手接怪、群体承压和第一轮打断。</v>
       </c>
       <c r="F2" t="str">
-        <v>起手用挑战怒吼稳定鱼人斥候，优先打断寒光先知治疗，再用复仇覆盖鱼人前排。</v>
+        <v>起手建立多目标仇恨，优先打断寒光先知治疗，并用范围仇恨覆盖鱼人前排。</v>
       </c>
       <c r="G2" t="str">
         <v>新仇旧恨</v>
@@ -597,7 +597,7 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur</v>
       </c>
       <c r="T2">
         <v>1</v>
@@ -609,7 +609,7 @@
         <v>balanced</v>
       </c>
       <c r="W2" t="str">
-        <v>warrior_t</v>
+        <v>warrior_t,druid_bear_t</v>
       </c>
       <c r="X2" t="str">
         <v>WestFall-1,WestFall-3</v>
@@ -647,13 +647,13 @@
         <v>狗头人法系和鱼人支援混合，要求在打断、控制和集火之间做取舍。</v>
       </c>
       <c r="F3" t="str">
-        <v>狗头人学徒的烛火飞弹和寒光先知治疗优先打断，队伍被点名时用挑战怒吼拉回仇恨。</v>
+        <v>优先打断狗头人学徒的烛火飞弹和寒光先知治疗；队伍被点名时及时用群体仇恨技能拉回目标。</v>
       </c>
       <c r="G3" t="str">
         <v>它们不喜欢你</v>
       </c>
       <c r="H3" t="str">
-        <v>你的队伍开场的三次攻击会产生5倍仇恨</v>
+        <v>你的队伍开场的三次攻击会产生2倍仇恨</v>
       </c>
       <c r="I3" t="str">
         <v>dislike_affix_pic</v>
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur</v>
       </c>
       <c r="T3">
         <v>1</v>
@@ -698,13 +698,13 @@
         <v>balanced</v>
       </c>
       <c r="W3" t="str">
-        <v>warrior_t</v>
+        <v>warrior_t,druid_bear_t</v>
       </c>
       <c r="X3" t="str">
         <v>RingingDeeps-3,RingingDeeps-6,WestFall-3</v>
       </c>
       <c r="Y3" t="str">
-        <v>狗头人武僧、狗头人学徒、鱼人吹箭者、寒光先知</v>
+        <v>狗头人武僧、狗头人学徒、鱼人猎潮者、寒光先知、狗头人拾荒者</v>
       </c>
       <c r="Z3" t="str">
         <v>standard_5slot</v>
@@ -736,7 +736,7 @@
         <v>围绕老瞎眼冲锋、鱼人法术和后排支援设计的高压短线挑战。</v>
       </c>
       <c r="F4" t="str">
-        <v>围绕老瞎眼冲锋安排盾墙或无视苦痛，优先击杀寒光智者，盾牌反射留给鱼人闪电术。</v>
+        <v>围绕老瞎眼冲锋安排主要减伤，优先击杀寒光智者，并为鱼人闪电术保留打断或法术应对。</v>
       </c>
       <c r="G4" t="str">
         <v>新仇旧恨</v>
@@ -775,7 +775,7 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur</v>
       </c>
       <c r="T4">
         <v>1</v>
@@ -787,22 +787,22 @@
         <v>expert</v>
       </c>
       <c r="W4" t="str">
-        <v>warrior_t</v>
+        <v>warrior_t,druid_bear_t</v>
       </c>
       <c r="X4" t="str">
         <v>WestFall-5,WestFall-6</v>
       </c>
       <c r="Y4" t="str">
-        <v>老瞎眼、寒光智者、寒光先知、鱼人领军、鱼人斥候</v>
+        <v>老瞎眼、寒光智者、鱼人领军、鱼人猎潮者、鱼人斥候</v>
       </c>
       <c r="Z4" t="str">
         <v>standard_5slot</v>
       </c>
       <c r="AA4" t="str">
-        <v>挑战怒吼,盾牌格挡,盾牌反射,无视苦痛,盾墙,盾牌猛击,复仇</v>
+        <v/>
       </c>
       <c r="AB4" t="str">
-        <v>加固板甲,野蛮训练,防御姿态,护卫神盾</v>
+        <v/>
       </c>
       <c r="AC4" t="str">
         <v>TRUE</v>
@@ -825,7 +825,7 @@
         <v>狗头人法术与鱼人标记交错出现，要求在打断和减伤之间分配节奏。</v>
       </c>
       <c r="F5" t="str">
-        <v>后排潮火期间优先打断法术读条，先击杀鱼人吹箭者或寒光智者，减伤留给标记后的集火窗口。</v>
+        <v>后排潮火期间优先打断法术读条，先击杀鱼人吹箭者或寒光智者，主要减伤留给标记后的集火窗口。</v>
       </c>
       <c r="G5" t="str">
         <v>潮火交错</v>
@@ -864,7 +864,7 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts</v>
       </c>
       <c r="T5">
         <v>2</v>
@@ -876,7 +876,7 @@
         <v>hard</v>
       </c>
       <c r="W5" t="str">
-        <v>warrior_t</v>
+        <v>warrior_t,druid_bear_t</v>
       </c>
       <c r="X5" t="str">
         <v>RingingDeeps-3,WestFall-4</v>
@@ -914,7 +914,7 @@
         <v>拾荒者和寒光支援制造分散压力，适合检验集火选择和反射窗口。</v>
       </c>
       <c r="F6" t="str">
-        <v>寒光智者的鱼人闪电术优先盾牌反射，寒光先知治疗和拾荒者拿下不要同时漏掉。</v>
+        <v>寒光智者的鱼人闪电术优先打断或使用法术应对；寒光先知治疗和拾荒者拿下不要同时漏掉。</v>
       </c>
       <c r="G6" t="str">
         <v>潮火交错</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts</v>
       </c>
       <c r="T6">
         <v>2</v>
@@ -965,7 +965,7 @@
         <v>hard</v>
       </c>
       <c r="W6" t="str">
-        <v>warrior_t</v>
+        <v>warrior_t,druid_bear_t</v>
       </c>
       <c r="X6" t="str">
         <v>RingingDeeps-5,WestFall-5</v>
@@ -977,10 +977,10 @@
         <v>8slot_0</v>
       </c>
       <c r="AA6" t="str">
-        <v>拳击,盾牌反射,无视苦痛,盾牌猛击,盾牌格挡</v>
+        <v/>
       </c>
       <c r="AB6" t="str">
-        <v>护卫神盾,野蛮训练</v>
+        <v/>
       </c>
       <c r="AC6" t="str">
         <v>TRUE</v>
@@ -1003,7 +1003,7 @@
         <v>蜡烛之王和鱼人领军带来机制链压力，但敌人数量控制在较小规模。</v>
       </c>
       <c r="F7" t="str">
-        <v>保持蜡像和暗影之锄命中同一目标，优先处理鱼人领军增益，盾牌反射留给寒光智者。</v>
+        <v>保持蜡像和暗影之锄命中同一目标，优先处理鱼人领军增益，并为寒光智者保留关键法术应对。</v>
       </c>
       <c r="G7" t="str">
         <v>蜡影号令</v>
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts</v>
       </c>
       <c r="T7">
         <v>2</v>
@@ -1054,7 +1054,7 @@
         <v>expert</v>
       </c>
       <c r="W7" t="str">
-        <v>warrior_t</v>
+        <v>warrior_t,druid_bear_t</v>
       </c>
       <c r="X7" t="str">
         <v>RingingDeeps-6,WestFall-6</v>
@@ -1066,10 +1066,10 @@
         <v>8slot_0</v>
       </c>
       <c r="AA7" t="str">
-        <v>挑战怒吼,风暴之锤,盾牌反射,无视苦痛,盾墙,盾牌猛击,复仇</v>
+        <v/>
       </c>
       <c r="AB7" t="str">
-        <v>加固板甲,防御姿态,护卫神盾,野蛮训练</v>
+        <v/>
       </c>
       <c r="AC7" t="str">
         <v>TRUE</v>
@@ -1092,7 +1092,7 @@
         <v>巨魔猎头者在后排制造破口，狂战士和吹箭者逼使玩家在接怪、控场和打断之间取舍。</v>
       </c>
       <c r="F8" t="str">
-        <v>优先击杀寒光先知或后排智者，复仇尽量覆盖后排两点；穿矛破口叠高后用盾牌格挡或盾墙。</v>
+        <v>优先击杀寒光先知或后排智者，范围仇恨尽量覆盖后排两点；穿矛破口叠高后使用物理减伤或主要减伤。</v>
       </c>
       <c r="G8" t="str">
         <v>穿矛破口</v>
@@ -1131,7 +1131,7 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts,druid_bear_t_lunar_beam,druid_bear_t_incarnation_ursoc,druid_bear_t_rage_of_the_sleeper,druid_bear_t_regrowth,druid_bear_t_berserk,druid_bear_t_roar</v>
       </c>
       <c r="T8">
         <v>3</v>
@@ -1143,7 +1143,7 @@
         <v>hard</v>
       </c>
       <c r="W8" t="str">
-        <v>warrior_t</v>
+        <v>warrior_t,druid_bear_t</v>
       </c>
       <c r="X8" t="str">
         <v>ZulAman-1,WestFall-3,RingingDeeps-3</v>
@@ -1155,10 +1155,10 @@
         <v>8slot_2</v>
       </c>
       <c r="AA8" t="str">
-        <v>挑战怒吼,拳击,盾牌格挡,无视苦痛,盾牌猛击</v>
+        <v/>
       </c>
       <c r="AB8" t="str">
-        <v>加固板甲,野蛮训练</v>
+        <v/>
       </c>
       <c r="AC8" t="str">
         <v>TRUE</v>
@@ -1181,7 +1181,7 @@
         <v>巨魔治疗、护盾和鱼人治疗交错出现，考验玩家能否在支援链形成前完成集火。</v>
       </c>
       <c r="F9" t="str">
-        <v>优先压制高阶牧师和寒光先知，药雾回甘会拖长巨魔单位存活时间，盾牌反射留给关键法术。</v>
+        <v>优先压制高阶牧师和寒光先知；药雾回甘会拖长巨魔单位存活时间，为关键法术保留打断或应对技能。</v>
       </c>
       <c r="G9" t="str">
         <v>药雾回甘</v>
@@ -1220,7 +1220,7 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts,druid_bear_t_lunar_beam,druid_bear_t_incarnation_ursoc,druid_bear_t_rage_of_the_sleeper,druid_bear_t_regrowth,druid_bear_t_berserk,druid_bear_t_roar</v>
       </c>
       <c r="T9">
         <v>3</v>
@@ -1232,7 +1232,7 @@
         <v>hard</v>
       </c>
       <c r="W9" t="str">
-        <v>warrior_t</v>
+        <v>warrior_t,druid_bear_t</v>
       </c>
       <c r="X9" t="str">
         <v>ZulAman-2,WestFall-3,WestFall-5</v>
@@ -1244,10 +1244,10 @@
         <v>8slot_2</v>
       </c>
       <c r="AA9" t="str">
-        <v>挑战怒吼,拳击,盾牌反射,无视苦痛,盾牌格挡,盾牌猛击</v>
+        <v/>
       </c>
       <c r="AB9" t="str">
-        <v>加固板甲,防御姿态,护卫神盾,野蛮训练</v>
+        <v/>
       </c>
       <c r="AC9" t="str">
         <v>TRUE</v>
@@ -1270,7 +1270,7 @@
         <v>巨魔督军与持盾卫士形成前排换防，后排牧师护盾会拖慢击杀节奏。</v>
       </c>
       <c r="F10" t="str">
-        <v>优先处理巨魔高阶牧师的护盾和治疗，盾阵换防触发后先转火或补减伤，盾墙留给督军撕裂窗口。</v>
+        <v>优先处理巨魔高阶牧师的护盾和治疗；盾阵换防触发后先转火或补减伤，主要减伤留给督军撕裂窗口。</v>
       </c>
       <c r="G10" t="str">
         <v>盾阵换防</v>
@@ -1309,7 +1309,7 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts,druid_bear_t_lunar_beam,druid_bear_t_incarnation_ursoc,druid_bear_t_rage_of_the_sleeper,druid_bear_t_regrowth,druid_bear_t_berserk,druid_bear_t_roar</v>
       </c>
       <c r="T10">
         <v>3</v>
@@ -1321,7 +1321,7 @@
         <v>hard</v>
       </c>
       <c r="W10" t="str">
-        <v>warrior_t</v>
+        <v>warrior_t,druid_bear_t</v>
       </c>
       <c r="X10" t="str">
         <v>ZulAman-3,WestFall-6</v>
@@ -1333,10 +1333,10 @@
         <v>8slot_2</v>
       </c>
       <c r="AA10" t="str">
-        <v>挑战怒吼,拳击,盾牌格挡,无视苦痛,盾墙,复仇</v>
+        <v/>
       </c>
       <c r="AB10" t="str">
-        <v>加固板甲,野蛮训练,防御姿态,护卫神盾</v>
+        <v/>
       </c>
       <c r="AC10" t="str">
         <v>TRUE</v>

--- a/public/designer-data/challenge_stage_content.xlsx
+++ b/public/designer-data/challenge_stage_content.xlsx
@@ -123,10 +123,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,10 +158,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -704,7 +704,7 @@
         <v>RingingDeeps-3,RingingDeeps-6,WestFall-3</v>
       </c>
       <c r="Y3" t="str">
-        <v>狗头人武僧、狗头人学徒、鱼人猎潮者、寒光先知、狗头人拾荒者</v>
+        <v>狗头人矿工、狗头人学徒、鱼人猎潮者、寒光先知、狗头人拾荒者</v>
       </c>
       <c r="Z3" t="str">
         <v>standard_5slot</v>
@@ -793,7 +793,7 @@
         <v>WestFall-5,WestFall-6</v>
       </c>
       <c r="Y4" t="str">
-        <v>老瞎眼、寒光智者、鱼人领军、鱼人猎潮者、鱼人斥候</v>
+        <v>老瞎眼、鱼人领军、鱼人猎潮者、鱼人斥候</v>
       </c>
       <c r="Z4" t="str">
         <v>standard_5slot</v>

--- a/public/designer-data/challenge_stage_content.xlsx
+++ b/public/designer-data/challenge_stage_content.xlsx
@@ -123,10 +123,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -158,10 +158,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -793,7 +793,7 @@
         <v>WestFall-5,WestFall-6</v>
       </c>
       <c r="Y4" t="str">
-        <v>老瞎眼、鱼人领军、鱼人猎潮者、鱼人斥候</v>
+        <v>老瞎眼、寒光先知、鱼人领军、鱼人猎潮者、鱼人斥候</v>
       </c>
       <c r="Z4" t="str">
         <v>standard_5slot</v>
@@ -864,7 +864,7 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_rage_of_the_sleeper</v>
       </c>
       <c r="T5">
         <v>2</v>
@@ -953,7 +953,7 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_rage_of_the_sleeper</v>
       </c>
       <c r="T6">
         <v>2</v>
@@ -1018,7 +1018,7 @@
         <v>潮汐军令</v>
       </c>
       <c r="K7" t="str">
-        <v>后排或鱼人单位成功造成伤害时，对目标施加潮汐破绽：受到伤害提高10%，至多5层。</v>
+        <v>后排或鱼人单位成功造成伤害时，对目标施加潮汐破绽：受到伤害提高18%，至多5层。</v>
       </c>
       <c r="L7" t="str">
         <v>challenge_tide_order</v>
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_rage_of_the_sleeper</v>
       </c>
       <c r="T7">
         <v>2</v>
@@ -1131,7 +1131,7 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts,druid_bear_t_lunar_beam,druid_bear_t_incarnation_ursoc,druid_bear_t_rage_of_the_sleeper,druid_bear_t_regrowth,druid_bear_t_berserk,druid_bear_t_roar</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_rage_of_the_sleeper,druid_bear_t_lunar_beam,druid_bear_t_incarnation_ursoc,druid_bear_t_survival_instincts,druid_bear_t_regrowth,druid_bear_t_berserk,druid_bear_t_roar</v>
       </c>
       <c r="T8">
         <v>3</v>
@@ -1220,7 +1220,7 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts,druid_bear_t_lunar_beam,druid_bear_t_incarnation_ursoc,druid_bear_t_rage_of_the_sleeper,druid_bear_t_regrowth,druid_bear_t_berserk,druid_bear_t_roar</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_rage_of_the_sleeper,druid_bear_t_lunar_beam,druid_bear_t_incarnation_ursoc,druid_bear_t_survival_instincts,druid_bear_t_regrowth,druid_bear_t_berserk,druid_bear_t_roar</v>
       </c>
       <c r="T9">
         <v>3</v>
@@ -1309,7 +1309,7 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_survival_instincts,druid_bear_t_lunar_beam,druid_bear_t_incarnation_ursoc,druid_bear_t_rage_of_the_sleeper,druid_bear_t_regrowth,druid_bear_t_berserk,druid_bear_t_roar</v>
+        <v>warrior_t_taunt,warrior_t_interrupt,warrior_t_stun,warrior_t_mass_taunt,warrior_t_shield_wall,warrior_t_revenge,warrior_t_ignore_pain,warrior_t_shield_block,warrior_t_shield_slam,warrior_t_shield_reflection,warrior_t_avatar,warrior_t_shockwave,warrior_t_thunderstruck,warrior_t_rallying_cry,warrior_t_intervene,warrior_t_demoralizing_shout,druid_bear_t_growl,druid_bear_t_mangle,druid_bear_t_thrash,druid_bear_t_skull_bash,druid_bear_t_ironfur,druid_bear_t_frenzied_regeneration,druid_bear_t_swipe,druid_bear_t_moonfire,druid_bear_t_barkskin,druid_bear_t_rage_of_the_sleeper,druid_bear_t_lunar_beam,druid_bear_t_incarnation_ursoc,druid_bear_t_survival_instincts,druid_bear_t_regrowth,druid_bear_t_berserk,druid_bear_t_roar</v>
       </c>
       <c r="T10">
         <v>3</v>
